--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 35,82</t>
+          <t>11,6; 36,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 27,52</t>
+          <t>-0,57; 27,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,53; -4,1</t>
+          <t>-41,63; -2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 34,98</t>
+          <t>9,39; 35,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 25,74</t>
+          <t>-3,57; 25,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,87; -9,06</t>
+          <t>-37,39; -7,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 32,85</t>
+          <t>14,17; 32,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 22,83</t>
+          <t>2,03; 22,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,12; -11,03</t>
+          <t>-35,57; -11,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,57; 67,45</t>
+          <t>16,2; 69,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 50,28</t>
+          <t>-0,92; 49,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,96; -5,15</t>
+          <t>-62,54; -3,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 63,46</t>
+          <t>13,42; 66,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 45,93</t>
+          <t>-5,11; 45,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,71; -16,28</t>
+          <t>-54,41; -12,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 59,01</t>
+          <t>20,71; 57,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 40,24</t>
+          <t>2,78; 39,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -17,59</t>
+          <t>-53,65; -19,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,51; 26,97</t>
+          <t>16,32; 26,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 11,0</t>
+          <t>-1,7; 10,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,29; -29,49</t>
+          <t>-44,46; -30,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 22,1</t>
+          <t>12,68; 22,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 10,69</t>
+          <t>-0,75; 9,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,66; -26,84</t>
+          <t>-38,74; -26,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 22,76</t>
+          <t>15,46; 22,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,78</t>
+          <t>0,91; 8,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -30,35</t>
+          <t>-39,48; -30,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 42,5</t>
+          <t>22,99; 41,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 17,34</t>
+          <t>-2,3; 16,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,27; -46,83</t>
+          <t>-63,38; -46,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,09; 34,34</t>
+          <t>17,82; 34,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 15,85</t>
+          <t>-1,0; 15,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,99; -40,29</t>
+          <t>-54,75; -39,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,31; 34,78</t>
+          <t>21,85; 34,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 13,48</t>
+          <t>1,29; 13,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,94; -45,39</t>
+          <t>-56,83; -45,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 21,88</t>
+          <t>8,47; 22,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 4,22</t>
+          <t>-14,03; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-63,51; -46,75</t>
+          <t>-62,66; -46,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,07; 28,99</t>
+          <t>14,3; 29,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 19,68</t>
+          <t>2,47; 19,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,72; -38,17</t>
+          <t>-56,3; -39,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,54; 23,54</t>
+          <t>13,7; 23,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,9</t>
+          <t>-3,3; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -45,3</t>
+          <t>-57,2; -45,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 30,52</t>
+          <t>10,4; 31,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 5,79</t>
+          <t>-17,01; 5,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,93; -62,11</t>
+          <t>-77,34; -62,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 44,62</t>
+          <t>18,47; 45,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 30,28</t>
+          <t>3,19; 28,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,82; -56,82</t>
+          <t>-75,25; -56,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,11; 33,13</t>
+          <t>17,5; 33,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 12,43</t>
+          <t>-4,17; 11,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,61; -61,9</t>
+          <t>-74,08; -62,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,1</t>
+          <t>16,24; 24,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,73</t>
+          <t>-0,84; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-45,28; -34,84</t>
+          <t>-45,07; -35,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,76</t>
+          <t>14,95; 22,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,92</t>
+          <t>2,19; 11,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -30,73</t>
+          <t>-40,16; -30,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,89; 22,53</t>
+          <t>16,84; 22,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,52</t>
+          <t>1,9; 8,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-41,07; -33,73</t>
+          <t>-41,24; -34,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,77; 36,14</t>
+          <t>22,31; 36,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 11,5</t>
+          <t>-1,2; 11,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -51,36</t>
+          <t>-63,41; -51,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 34,68</t>
+          <t>20,83; 34,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,38</t>
+          <t>3,19; 17,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -45,93</t>
+          <t>-56,98; -45,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,7; 33,57</t>
+          <t>23,69; 33,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,57</t>
+          <t>2,69; 11,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,4; -50,11</t>
+          <t>-58,61; -50,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 36,82</t>
+          <t>11,75; 36,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 27,23</t>
+          <t>-2,0; 28,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -2,15</t>
+          <t>-41,55; -0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 35,82</t>
+          <t>11,35; 35,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 25,36</t>
+          <t>-4,04; 24,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,39; -7,14</t>
+          <t>-37,34; -7,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 32,39</t>
+          <t>13,65; 32,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 22,59</t>
+          <t>1,91; 23,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-35,57; -11,48</t>
+          <t>-36,14; -11,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,2; 69,37</t>
+          <t>17,32; 70,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 49,49</t>
+          <t>-3,17; 51,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,54; -3,48</t>
+          <t>-63,0; 0,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 66,1</t>
+          <t>15,51; 63,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 45,91</t>
+          <t>-5,69; 43,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -12,48</t>
+          <t>-53,81; -14,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 57,12</t>
+          <t>18,52; 56,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 39,83</t>
+          <t>2,64; 40,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,65; -19,01</t>
+          <t>-54,08; -19,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 26,67</t>
+          <t>16,43; 27,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 10,43</t>
+          <t>-0,37; 11,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -30,49</t>
+          <t>-43,42; -30,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 22,34</t>
+          <t>12,53; 22,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 9,76</t>
+          <t>-0,46; 10,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,74; -26,76</t>
+          <t>-39,1; -27,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,46; 22,7</t>
+          <t>16,06; 23,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,85</t>
+          <t>0,87; 8,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -30,07</t>
+          <t>-39,69; -30,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,99; 41,93</t>
+          <t>23,49; 42,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 16,63</t>
+          <t>-0,58; 17,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,38; -46,91</t>
+          <t>-62,46; -47,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 34,21</t>
+          <t>17,33; 35,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 15,1</t>
+          <t>-0,68; 16,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -39,78</t>
+          <t>-55,55; -41,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 34,51</t>
+          <t>22,63; 35,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,64</t>
+          <t>1,28; 13,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,83; -45,61</t>
+          <t>-57,03; -45,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 22,61</t>
+          <t>9,19; 23,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 3,84</t>
+          <t>-13,56; 3,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-62,66; -46,53</t>
+          <t>-62,64; -46,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 29,98</t>
+          <t>13,11; 28,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 19,08</t>
+          <t>2,5; 18,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,3; -39,07</t>
+          <t>-56,31; -39,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,7; 23,54</t>
+          <t>13,13; 23,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,22</t>
+          <t>-3,58; 8,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-57,2; -45,22</t>
+          <t>-56,83; -45,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,4; 31,31</t>
+          <t>11,23; 31,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 5,01</t>
+          <t>-16,59; 4,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,34; -62,03</t>
+          <t>-77,51; -62,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 45,85</t>
+          <t>16,97; 43,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 28,63</t>
+          <t>3,35; 28,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -56,89</t>
+          <t>-73,74; -56,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 33,19</t>
+          <t>16,5; 32,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 11,35</t>
+          <t>-4,61; 11,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,08; -62,35</t>
+          <t>-73,82; -61,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,16</t>
+          <t>16,71; 24,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,93</t>
+          <t>-0,83; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-45,07; -35,22</t>
+          <t>-45,46; -35,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,95; 22,75</t>
+          <t>14,87; 23,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,4</t>
+          <t>2,38; 11,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -30,72</t>
+          <t>-40,55; -31,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,39</t>
+          <t>16,88; 22,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,06</t>
+          <t>1,87; 7,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -34,05</t>
+          <t>-41,14; -34,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,31; 36,13</t>
+          <t>23,23; 37,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 11,88</t>
+          <t>-1,16; 12,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,41; -51,8</t>
+          <t>-63,68; -52,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,83; 34,33</t>
+          <t>20,68; 35,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,39</t>
+          <t>3,41; 16,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -45,79</t>
+          <t>-57,48; -46,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,69; 33,24</t>
+          <t>23,74; 33,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 11,85</t>
+          <t>2,65; 11,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,61; -50,07</t>
+          <t>-58,55; -50,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-23,11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>23,95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>14,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-25,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,35</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-24,16</t>
+          <t>-27,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-24,48</t>
+          <t>-24,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 36,46</t>
+          <t>10,13; 34,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 28,44</t>
+          <t>-4,21; 25,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -0,2</t>
+          <t>-36,81; -7,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 35,18</t>
+          <t>10,4; 35,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 24,47</t>
+          <t>-2,07; 27,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,34; -7,92</t>
+          <t>-40,92; -11,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,65; 32,01</t>
+          <t>13,57; 32,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 23,5</t>
+          <t>2,13; 22,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-36,14; -11,88</t>
+          <t>-36,59; -13,37</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-36,03%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>38,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>22,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-40,18%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-37,68%</t>
+          <t>-43,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,74%</t>
+          <t>-39,2%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,32; 70,94</t>
+          <t>14,48; 63,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 51,86</t>
+          <t>-6,02; 45,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 0,32</t>
+          <t>-52,81; -13,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 63,3</t>
+          <t>15,57; 67,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 43,2</t>
+          <t>-2,95; 50,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,81; -14,38</t>
+          <t>-62,28; -22,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 56,03</t>
+          <t>19,66; 59,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 40,42</t>
+          <t>3,04; 40,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,08; -19,36</t>
+          <t>-53,12; -22,5</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-32,29</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>21,86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,26</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-36,38</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-33,18</t>
+          <t>-34,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-34,69</t>
+          <t>-33,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 27,13</t>
+          <t>12,22; 22,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 11,19</t>
+          <t>-0,94; 10,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,42; -30,6</t>
+          <t>-37,82; -26,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 22,8</t>
+          <t>16,51; 26,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 10,76</t>
+          <t>-0,55; 11,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -27,06</t>
+          <t>-39,37; -28,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 23,36</t>
+          <t>15,55; 22,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,87</t>
+          <t>0,55; 8,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -30,38</t>
+          <t>-37,44; -29,17</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-47,22%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-54,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-48,52%</t>
+          <t>-50,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-51,12%</t>
+          <t>-48,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 42,92</t>
+          <t>17,09; 34,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 17,42</t>
+          <t>-1,48; 15,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,46; -47,03</t>
+          <t>-54,06; -39,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 35,25</t>
+          <t>23,12; 42,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 16,62</t>
+          <t>-0,82; 17,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -41,05</t>
+          <t>-56,49; -43,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,63; 35,56</t>
+          <t>22,31; 34,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,57</t>
+          <t>0,81; 13,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,03; -45,84</t>
+          <t>-53,38; -43,67</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,66</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-46,91</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>15,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,97</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-54,69</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21,56</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,66</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-47,87</t>
+          <t>-55,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-51,39</t>
+          <t>-51,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,19; 23,13</t>
+          <t>14,07; 28,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 3,04</t>
+          <t>2,36; 19,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-62,64; -46,39</t>
+          <t>-55,49; -36,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,11; 28,36</t>
+          <t>8,21; 21,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 18,93</t>
+          <t>-12,78; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,31; -39,07</t>
+          <t>-63,89; -46,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,13; 23,15</t>
+          <t>13,54; 23,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 8,23</t>
+          <t>-2,88; 8,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-56,83; -45,22</t>
+          <t>-56,83; -44,79</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29,91%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14,79%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-65,07%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-6,35%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-69,96%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-66,4%</t>
+          <t>-70,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-68,27%</t>
+          <t>-67,87%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 31,94</t>
+          <t>18,65; 44,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 4,16</t>
+          <t>3,18; 30,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,51; -62,09</t>
+          <t>-73,7; -55,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,97; 43,05</t>
+          <t>10,36; 30,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 28,81</t>
+          <t>-15,82; 5,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,74; -56,78</t>
+          <t>-78,31; -62,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,5; 32,3</t>
+          <t>17,11; 33,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 11,39</t>
+          <t>-3,79; 12,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-73,82; -61,88</t>
+          <t>-73,53; -61,6</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,08</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-34,96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>20,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-39,92</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19,08</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-35,89</t>
+          <t>-38,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-37,79</t>
+          <t>-36,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,71; 24,87</t>
+          <t>14,65; 22,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,19</t>
+          <t>1,75; 10,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-45,46; -35,23</t>
+          <t>-39,27; -29,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,31</t>
+          <t>16,35; 24,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,13</t>
+          <t>-1,32; 7,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -31,04</t>
+          <t>-43,26; -33,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,27</t>
+          <t>16,89; 22,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,94</t>
+          <t>1,89; 8,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -34,26</t>
+          <t>-39,86; -33,09</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-50,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>29,07%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-57,3%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,14%</t>
+          <t>-55,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-54,57%</t>
+          <t>-53,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,23; 37,78</t>
+          <t>20,51; 34,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 12,21</t>
+          <t>2,44; 16,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,68; -52,06</t>
+          <t>-56,01; -44,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,68; 35,26</t>
+          <t>22,77; 36,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,93</t>
+          <t>-1,87; 11,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,48; -46,15</t>
+          <t>-60,36; -50,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,12</t>
+          <t>23,7; 33,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,78</t>
+          <t>2,68; 12,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,55; -50,42</t>
+          <t>-56,41; -48,89</t>
         </is>
       </c>
     </row>
